--- a/Excel/v5/UKRR DataSet Amendments_30Apr2026.xlsx
+++ b/Excel/v5/UKRR DataSet Amendments_30Apr2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marta.badji\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB1A90D-D5A4-4DFD-B512-020405ADE35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1A85E5-D4D3-4926-A034-C669B2A91B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Amendments" sheetId="21" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Amendments!$C$1:$K$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Amendments!$C$1:$J$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="132">
   <si>
     <t>Format</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Unit of Measurement</t>
   </si>
   <si>
-    <t xml:space="preserve"> Range</t>
-  </si>
-  <si>
     <t>IF / Qualification</t>
   </si>
   <si>
@@ -185,9 +182,6 @@
     <t>nn.n</t>
   </si>
   <si>
-    <t>0  -  90</t>
-  </si>
-  <si>
     <t>Glomerular filtration rate (GFR) predicted by creatinine based formula (CKD-EPI) WITHOUT ethnicity</t>
   </si>
   <si>
@@ -203,27 +197,18 @@
     <t>White blood count (WBC)</t>
   </si>
   <si>
-    <t>0.1  -  30.0</t>
-  </si>
-  <si>
     <t>QBLE4</t>
   </si>
   <si>
     <t>Platelets</t>
   </si>
   <si>
-    <t>100  -  600</t>
-  </si>
-  <si>
     <t>QBLJJ</t>
   </si>
   <si>
     <t>QBLF3</t>
   </si>
   <si>
-    <t>1  -  70</t>
-  </si>
-  <si>
     <t>QBLC1</t>
   </si>
   <si>
@@ -233,9 +218,6 @@
     <t>Urine protein:creatinine ratio</t>
   </si>
   <si>
-    <t>0.0  -  2000</t>
-  </si>
-  <si>
     <t>QBLC3</t>
   </si>
   <si>
@@ -297,9 +279,6 @@
   </si>
   <si>
     <t>UKRDC / RDA Mapping</t>
-  </si>
-  <si>
-    <t>1 - 9</t>
   </si>
   <si>
     <t>mL/min/1.72m^2</t>
@@ -442,6 +421,18 @@
   </si>
   <si>
     <t>PV data items</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+  </si>
+  <si>
+    <t>Ranges removed</t>
+  </si>
+  <si>
+    <t>Observations</t>
+  </si>
+  <si>
+    <t>Lab Results</t>
   </si>
 </sst>
 </file>
@@ -634,7 +625,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -652,7 +643,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -749,6 +739,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -766,9 +759,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1163,7 +1153,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.1640625" customWidth="1"/>
@@ -1173,30 +1163,29 @@
     <col min="6" max="6" width="46.58203125" customWidth="1"/>
     <col min="7" max="7" width="41.58203125" customWidth="1"/>
     <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="10.58203125" customWidth="1"/>
-    <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="25.08203125" customWidth="1"/>
-    <col min="12" max="12" width="36" customWidth="1"/>
-    <col min="13" max="13" width="163.33203125" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="25.08203125" customWidth="1"/>
+    <col min="11" max="11" width="36" customWidth="1"/>
+    <col min="12" max="12" width="163.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:11" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="31" x14ac:dyDescent="0.35">
-      <c r="A3" s="54" t="s">
-        <v>132</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="31" x14ac:dyDescent="0.35">
+      <c r="A3" s="47" t="s">
+        <v>125</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>0</v>
@@ -1210,1097 +1199,1081 @@
       <c r="H3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>5.2</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="30"/>
+      <c r="I4" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="48" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="31" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>5.2</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="30"/>
+      <c r="I5" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="49"/>
+    </row>
+    <row r="6" spans="1:11" ht="155" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5.2</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="30"/>
+      <c r="I6" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="49"/>
+    </row>
+    <row r="7" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>5.2</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="33"/>
+      <c r="I7" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="49"/>
+    </row>
+    <row r="8" spans="1:11" ht="93" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5.2</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="49"/>
+    </row>
+    <row r="9" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>5.2</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="F9" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="49"/>
+    </row>
+    <row r="10" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>5.2</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="27"/>
+      <c r="E10" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="49"/>
+    </row>
+    <row r="11" spans="1:11" ht="31" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>5.2</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="27"/>
+      <c r="E11" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="49"/>
+    </row>
+    <row r="12" spans="1:11" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>5.2</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="27"/>
+      <c r="E12" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="38"/>
+      <c r="I12" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="49"/>
+    </row>
+    <row r="13" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>5.2</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="27"/>
+      <c r="E13" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="38"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="49"/>
+    </row>
+    <row r="14" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>5.2</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="36"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" s="50"/>
+    </row>
+    <row r="15" spans="1:11" ht="31" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>5.2</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="16"/>
+      <c r="I15" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="51" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="31" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>5.2</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="16"/>
+      <c r="I16" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" s="52"/>
+    </row>
+    <row r="17" spans="1:11" ht="155" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>5.2</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="16"/>
+      <c r="I17" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="52"/>
+    </row>
+    <row r="18" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>5.2</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="D18" s="13"/>
+      <c r="E18" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="19"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="52"/>
+    </row>
+    <row r="19" spans="1:11" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>5.2</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="52"/>
+    </row>
+    <row r="20" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>5.2</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K20" s="53"/>
+    </row>
+    <row r="21" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>5.2</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="51" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>5.2</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="48" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="31" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>5.2</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="K5" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="49"/>
-    </row>
-    <row r="6" spans="1:12" ht="155" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>5.2</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="28" t="s">
+    <row r="22" spans="1:11" ht="31" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>5.2</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="13"/>
+      <c r="E22" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" s="52"/>
+    </row>
+    <row r="23" spans="1:11" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>5.2</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="G6" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="L6" s="49"/>
-    </row>
-    <row r="7" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>5.2</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="34"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="L7" s="49"/>
-    </row>
-    <row r="8" spans="1:12" ht="93" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>5.2</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="K8" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="49"/>
-    </row>
-    <row r="9" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>5.2</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28" t="s">
+      <c r="H23" s="24"/>
+      <c r="I23" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="52"/>
+    </row>
+    <row r="24" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>5.2</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="49"/>
-    </row>
-    <row r="10" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>5.2</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="37" t="s">
+      <c r="F24" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="24"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10" s="49"/>
-    </row>
-    <row r="11" spans="1:12" ht="31" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>5.2</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="L11" s="49"/>
-    </row>
-    <row r="12" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>5.2</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="28"/>
-      <c r="E12" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="39"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="L12" s="49"/>
-    </row>
-    <row r="13" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>5.2</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="39"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="L13" s="49"/>
-    </row>
-    <row r="14" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>5.2</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" s="28" t="s">
+      <c r="K24" s="52"/>
+    </row>
+    <row r="25" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>5.2</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="13"/>
+      <c r="E25" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="37"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="L14" s="50"/>
-    </row>
-    <row r="15" spans="1:12" ht="31" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>5.2</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="K15" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="L15" s="51" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="31" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>5.2</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="K16" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="L16" s="52"/>
-    </row>
-    <row r="17" spans="1:12" ht="155" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>5.2</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="K17" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="L17" s="52"/>
-    </row>
-    <row r="18" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>5.2</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="20"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="L18" s="52"/>
-    </row>
-    <row r="19" spans="1:12" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>5.2</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="K19" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="L19" s="52"/>
-    </row>
-    <row r="20" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>5.2</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" s="14" t="s">
+      <c r="G25" s="22"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="K25" s="53"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>5.2</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>106</v>
-      </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="L20" s="53"/>
-    </row>
-    <row r="21" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>5.2</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="L21" s="51" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="31" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>5.2</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="K22" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="L22" s="52"/>
-    </row>
-    <row r="23" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>5.2</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="G23" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="H23" s="25"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="K23" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="L23" s="52"/>
-    </row>
-    <row r="24" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>5.2</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H24" s="25"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="L24" s="52"/>
-    </row>
-    <row r="25" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>5.2</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="G25" s="23"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="L25" s="53"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>5.2</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>113</v>
       </c>
       <c r="C26" s="7">
         <v>763264000</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E26" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K26" s="6"/>
+    </row>
+    <row r="27" spans="1:11" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>5.2</v>
+      </c>
+      <c r="B27" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" s="41"/>
+      <c r="H27" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I27" s="42"/>
+      <c r="J27" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="K27" s="45" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="31" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>5.2</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="46"/>
+      <c r="E28" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F28" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="G28" s="41"/>
+      <c r="H28" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I28" s="42"/>
+      <c r="J28" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="K28" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="J26" s="8"/>
-      <c r="K26" s="6" t="s">
+    </row>
+    <row r="29" spans="1:11" ht="31" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>5.2</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="46"/>
+      <c r="E29" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="41"/>
+      <c r="H29" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I29" s="42"/>
+      <c r="J29" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="L26" s="6"/>
-    </row>
-    <row r="27" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>5.2</v>
-      </c>
-      <c r="B27" s="44" t="s">
+      <c r="K29" s="44" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>5.2</v>
+      </c>
+      <c r="B30" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="46"/>
+      <c r="E30" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="41"/>
+      <c r="H30" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I30" s="42"/>
+      <c r="J30" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="K30" s="44" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>5.2</v>
+      </c>
+      <c r="B31" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="46"/>
+      <c r="E31" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="41"/>
+      <c r="H31" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I31" s="42"/>
+      <c r="J31" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="K31" s="44" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>5.2</v>
+      </c>
+      <c r="B32" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="46"/>
+      <c r="E32" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="G32" s="41"/>
+      <c r="H32" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I32" s="42"/>
+      <c r="J32" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="K32" s="44" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>5.2</v>
+      </c>
+      <c r="B33" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="46"/>
+      <c r="E33" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F33" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="G33" s="41"/>
+      <c r="H33" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="I33" s="42"/>
+      <c r="J33" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="K33" s="44" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>5.2</v>
+      </c>
+      <c r="B34" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D34" s="46"/>
+      <c r="E34" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F34" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="G34" s="41"/>
+      <c r="H34" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="I34" s="42"/>
+      <c r="J34" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="K34" s="44" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>5.2</v>
+      </c>
+      <c r="B35" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" s="46"/>
+      <c r="E35" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F35" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="I35" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="J35" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="K35" s="44" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>5.2</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>5.2</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>5.2</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>5.2</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>5.2</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="26"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>5.2</v>
+      </c>
+      <c r="B41" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="C27" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F27" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="G27" s="42"/>
-      <c r="H27" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="J27" s="43"/>
-      <c r="K27" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="L27" s="46" t="s">
+      <c r="C41" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>5.2</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" s="27" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" ht="31" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>5.2</v>
-      </c>
-      <c r="B28" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D28" s="47"/>
-      <c r="E28" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="G28" s="42"/>
-      <c r="H28" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J28" s="43"/>
-      <c r="K28" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="L28" s="45" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="31" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>5.2</v>
-      </c>
-      <c r="B29" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="47"/>
-      <c r="E29" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F29" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="G29" s="42"/>
-      <c r="H29" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J29" s="43"/>
-      <c r="K29" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="L29" s="45" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>5.2</v>
-      </c>
-      <c r="B30" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" s="47"/>
-      <c r="E30" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F30" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30" s="42"/>
-      <c r="H30" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="J30" s="43"/>
-      <c r="K30" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="L30" s="45" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>5.2</v>
-      </c>
-      <c r="B31" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31" s="47"/>
-      <c r="E31" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F31" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="G31" s="42"/>
-      <c r="H31" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="J31" s="43"/>
-      <c r="K31" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="L31" s="45" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>5.2</v>
-      </c>
-      <c r="B32" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D32" s="47"/>
-      <c r="E32" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="G32" s="42"/>
-      <c r="H32" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="I32" s="11"/>
-      <c r="J32" s="43"/>
-      <c r="K32" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="L32" s="45" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>5.2</v>
-      </c>
-      <c r="B33" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33" s="47"/>
-      <c r="E33" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F33" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="G33" s="42"/>
-      <c r="H33" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="J33" s="43"/>
-      <c r="K33" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="L33" s="45" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>5.2</v>
-      </c>
-      <c r="B34" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D34" s="47"/>
-      <c r="E34" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F34" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="G34" s="42"/>
-      <c r="H34" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="J34" s="43"/>
-      <c r="K34" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="L34" s="45" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>5.2</v>
-      </c>
-      <c r="B35" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D35" s="47"/>
-      <c r="E35" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F35" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="G35" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="I35" s="11"/>
-      <c r="J35" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="K35" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="L35" s="45" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>5.2</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>5.2</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13" t="s">
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B44" s="5" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>5.2</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13" t="s">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B45" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>5.2</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="13" t="s">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B46" s="39" t="s">
         <v>121</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>5.2</v>
-      </c>
-      <c r="B40" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="C40" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B42" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B43" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B44" s="40" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="L4:L14"/>
-    <mergeCell ref="L15:L20"/>
-    <mergeCell ref="L21:L25"/>
+    <mergeCell ref="K4:K14"/>
+    <mergeCell ref="K15:K20"/>
+    <mergeCell ref="K21:K25"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G4" r:id="rId1" xr:uid="{F1EC2680-9018-4C74-B22B-CD92FC568C41}"/>
